--- a/src/results/chile/cross_tab_wage.xlsx
+++ b/src/results/chile/cross_tab_wage.xlsx
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="C3" t="n">
-        <v>104</v>
-      </c>
-      <c r="D3" t="n">
-        <v>73</v>
-      </c>
-      <c r="E3" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>718</v>
+        <v>438</v>
       </c>
       <c r="D4" t="n">
-        <v>771</v>
+        <v>479</v>
       </c>
       <c r="E4" t="n">
-        <v>409</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -525,17 +525,17 @@
           <t>P Comp -15</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>35</v>
+      <c r="B5" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="D5" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>1148</v>
+        <v>698</v>
       </c>
       <c r="D6" t="n">
-        <v>1020</v>
+        <v>518</v>
       </c>
       <c r="E6" t="n">
-        <v>572</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>69</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
         <v>158</v>
       </c>
-      <c r="C7" t="n">
-        <v>742</v>
-      </c>
-      <c r="D7" t="n">
-        <v>484</v>
-      </c>
       <c r="E7" t="n">
-        <v>222</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="C8" t="n">
-        <v>1311</v>
+        <v>891</v>
       </c>
       <c r="D8" t="n">
-        <v>839</v>
+        <v>466</v>
       </c>
       <c r="E8" t="n">
-        <v>411</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>771</v>
+        <v>531</v>
       </c>
       <c r="C9" t="n">
-        <v>3061</v>
+        <v>2077</v>
       </c>
       <c r="D9" t="n">
-        <v>1741</v>
+        <v>1101</v>
       </c>
       <c r="E9" t="n">
-        <v>935</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>942</v>
+        <v>755</v>
       </c>
       <c r="C10" t="n">
-        <v>3848</v>
+        <v>3366</v>
       </c>
       <c r="D10" t="n">
-        <v>2108</v>
+        <v>1758</v>
       </c>
       <c r="E10" t="n">
-        <v>1048</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C11" t="n">
-        <v>3652</v>
+        <v>3769</v>
       </c>
       <c r="D11" t="n">
-        <v>1385</v>
+        <v>1798</v>
       </c>
       <c r="E11" t="n">
-        <v>659</v>
+        <v>876</v>
       </c>
     </row>
     <row r="12">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>559</v>
+        <v>506</v>
       </c>
       <c r="C12" t="n">
-        <v>2634</v>
+        <v>2889</v>
       </c>
       <c r="D12" t="n">
-        <v>952</v>
+        <v>1165</v>
       </c>
       <c r="E12" t="n">
-        <v>494</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14">
@@ -710,16 +710,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" t="n">
-        <v>61</v>
-      </c>
-      <c r="D16" t="n">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>451</v>
+        <v>265</v>
       </c>
       <c r="D17" t="n">
-        <v>488</v>
+        <v>278</v>
       </c>
       <c r="E17" t="n">
-        <v>223</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18">
@@ -747,17 +747,17 @@
           <t>P Comp -15</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>28</v>
+      <c r="B18" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="C19" t="n">
-        <v>689</v>
+        <v>427</v>
       </c>
       <c r="D19" t="n">
-        <v>773</v>
+        <v>369</v>
       </c>
       <c r="E19" t="n">
-        <v>374</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>470</v>
+        <v>161</v>
       </c>
       <c r="D20" t="n">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="E20" t="n">
-        <v>187</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="C21" t="n">
-        <v>793</v>
+        <v>585</v>
       </c>
       <c r="D21" t="n">
-        <v>568</v>
+        <v>336</v>
       </c>
       <c r="E21" t="n">
-        <v>319</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22">
@@ -824,16 +824,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>725</v>
+        <v>503</v>
       </c>
       <c r="C22" t="n">
-        <v>1973</v>
+        <v>1339</v>
       </c>
       <c r="D22" t="n">
-        <v>1357</v>
+        <v>780</v>
       </c>
       <c r="E22" t="n">
-        <v>776</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23">
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>958</v>
+        <v>762</v>
       </c>
       <c r="C23" t="n">
-        <v>2541</v>
+        <v>2271</v>
       </c>
       <c r="D23" t="n">
-        <v>1705</v>
+        <v>1505</v>
       </c>
       <c r="E23" t="n">
-        <v>941</v>
+        <v>910</v>
       </c>
     </row>
     <row r="24">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="C24" t="n">
-        <v>2709</v>
+        <v>2905</v>
       </c>
       <c r="D24" t="n">
-        <v>1273</v>
+        <v>1676</v>
       </c>
       <c r="E24" t="n">
-        <v>858</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="25">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>683</v>
+        <v>579</v>
       </c>
       <c r="C25" t="n">
-        <v>1965</v>
+        <v>2092</v>
       </c>
       <c r="D25" t="n">
-        <v>911</v>
+        <v>1077</v>
       </c>
       <c r="E25" t="n">
-        <v>722</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C31" t="n">
-        <v>38</v>
-      </c>
-      <c r="D31" t="n">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>198</v>
+        <v>126</v>
       </c>
       <c r="D32" t="n">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="E32" t="n">
-        <v>154</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
@@ -1007,17 +1007,17 @@
           <t>S Inc -15</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>45</v>
+      <c r="B33" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>95</v>
-      </c>
-      <c r="E33" t="n">
-        <v>45</v>
+        <v>26</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C34" t="n">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="D34" t="n">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="E34" t="n">
-        <v>118</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="C35" t="n">
-        <v>708</v>
+        <v>462</v>
       </c>
       <c r="D35" t="n">
-        <v>464</v>
+        <v>275</v>
       </c>
       <c r="E35" t="n">
-        <v>267</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36">
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>545</v>
+        <v>455</v>
       </c>
       <c r="C36" t="n">
-        <v>1054</v>
+        <v>1210</v>
       </c>
       <c r="D36" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E36" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C37" t="n">
-        <v>1537</v>
+        <v>1790</v>
       </c>
       <c r="D37" t="n">
-        <v>659</v>
+        <v>930</v>
       </c>
       <c r="E37" t="n">
-        <v>424</v>
+        <v>616</v>
       </c>
     </row>
     <row r="38">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C38" t="n">
-        <v>1356</v>
+        <v>1543</v>
       </c>
       <c r="D38" t="n">
-        <v>535</v>
+        <v>812</v>
       </c>
       <c r="E38" t="n">
-        <v>463</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C43" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="D43" t="n">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="E43" t="n">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C44" t="n">
-        <v>60</v>
-      </c>
-      <c r="D44" t="n">
-        <v>55</v>
-      </c>
-      <c r="E44" t="n">
-        <v>24</v>
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -1211,16 +1211,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C45" t="n">
-        <v>392</v>
+        <v>223</v>
       </c>
       <c r="D45" t="n">
-        <v>474</v>
+        <v>247</v>
       </c>
       <c r="E45" t="n">
-        <v>218</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46">
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C46" t="n">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="E46" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="C47" t="n">
-        <v>564</v>
+        <v>345</v>
       </c>
       <c r="D47" t="n">
-        <v>418</v>
+        <v>223</v>
       </c>
       <c r="E47" t="n">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>680</v>
+        <v>358</v>
       </c>
       <c r="C48" t="n">
-        <v>1429</v>
+        <v>902</v>
       </c>
       <c r="D48" t="n">
-        <v>1082</v>
+        <v>579</v>
       </c>
       <c r="E48" t="n">
-        <v>660</v>
+        <v>398</v>
       </c>
     </row>
     <row r="49">
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1022</v>
+        <v>759</v>
       </c>
       <c r="C49" t="n">
-        <v>2098</v>
+        <v>1911</v>
       </c>
       <c r="D49" t="n">
-        <v>1457</v>
+        <v>1289</v>
       </c>
       <c r="E49" t="n">
-        <v>829</v>
+        <v>791</v>
       </c>
     </row>
     <row r="50">
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>927</v>
+        <v>1001</v>
       </c>
       <c r="C50" t="n">
-        <v>2488</v>
+        <v>2870</v>
       </c>
       <c r="D50" t="n">
-        <v>1254</v>
+        <v>1640</v>
       </c>
       <c r="E50" t="n">
-        <v>771</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="51">
@@ -1325,16 +1325,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>741</v>
+        <v>766</v>
       </c>
       <c r="C51" t="n">
-        <v>1855</v>
+        <v>2131</v>
       </c>
       <c r="D51" t="n">
-        <v>848</v>
+        <v>1134</v>
       </c>
       <c r="E51" t="n">
-        <v>602</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -1384,17 +1384,17 @@
           <t>P Inc -15</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>33</v>
+      <c r="B2" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>139</v>
-      </c>
-      <c r="E2" t="n">
-        <v>83</v>
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C3" t="n">
-        <v>1472</v>
+        <v>889</v>
       </c>
       <c r="D3" t="n">
-        <v>1645</v>
+        <v>1002</v>
       </c>
       <c r="E3" t="n">
-        <v>787</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4">
@@ -1423,16 +1423,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>527</v>
+        <v>148</v>
       </c>
       <c r="D4" t="n">
-        <v>445</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>263</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>431</v>
+        <v>265</v>
       </c>
       <c r="C5" t="n">
-        <v>2427</v>
+        <v>1474</v>
       </c>
       <c r="D5" t="n">
-        <v>2518</v>
+        <v>1272</v>
       </c>
       <c r="E5" t="n">
-        <v>1318</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6">
@@ -1461,16 +1461,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>177</v>
       </c>
       <c r="C6" t="n">
-        <v>1575</v>
+        <v>582</v>
       </c>
       <c r="D6" t="n">
-        <v>1042</v>
+        <v>347</v>
       </c>
       <c r="E6" t="n">
-        <v>549</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -1480,16 +1480,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>803</v>
+        <v>568</v>
       </c>
       <c r="C7" t="n">
-        <v>2972</v>
+        <v>2019</v>
       </c>
       <c r="D7" t="n">
-        <v>2039</v>
+        <v>1144</v>
       </c>
       <c r="E7" t="n">
-        <v>1085</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2470</v>
+        <v>1545</v>
       </c>
       <c r="C8" t="n">
-        <v>7171</v>
+        <v>4780</v>
       </c>
       <c r="D8" t="n">
-        <v>4644</v>
+        <v>2735</v>
       </c>
       <c r="E8" t="n">
-        <v>2638</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="9">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3467</v>
+        <v>2731</v>
       </c>
       <c r="C9" t="n">
-        <v>9541</v>
+        <v>8758</v>
       </c>
       <c r="D9" t="n">
-        <v>5989</v>
+        <v>5272</v>
       </c>
       <c r="E9" t="n">
-        <v>3255</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="10">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3184</v>
+        <v>3230</v>
       </c>
       <c r="C10" t="n">
-        <v>10386</v>
+        <v>11334</v>
       </c>
       <c r="D10" t="n">
-        <v>4571</v>
+        <v>6044</v>
       </c>
       <c r="E10" t="n">
-        <v>2712</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="11">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2545</v>
+        <v>2403</v>
       </c>
       <c r="C11" t="n">
-        <v>7810</v>
+        <v>8655</v>
       </c>
       <c r="D11" t="n">
-        <v>3246</v>
+        <v>4188</v>
       </c>
       <c r="E11" t="n">
-        <v>2281</v>
+        <v>2701</v>
       </c>
     </row>
   </sheetData>
